--- a/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Côme aide papa au jardin. Les fleurs sentent fort. Le pollen chatouille le nez de Côme. Son nez coule un peu. Papa ouvre la poche de son manteau. Papa tend un mouchoir. Côme prend un mouchoir. Le papier est doux. Il se mouche. Atchoum, tout doux. L'air passe mieux. Papa dit : mouchoir, puis poubelle. Côme va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Côme se lave les mains au robinet. L'eau est fraîche. Papa dit : merci. Parce qu'il a pris un mouchoir, Côme respire mieux. Parce qu'il a jeté à la poubelle, ses mains sont prêtes à jouer. Ils arrosent les tomates. Côme sourit.</t>
+          <t>Côme aide papa au jardin. Les fleurs sentent fort. Le pollen chatouille le nez de Côme. Son nez coule un peu. Papa ouvre la poche de son manteau. Papa tend un mouchoir. Côme prend un mouchoir. Le papier est doux. Il se mouche. Atchoum, tout doux. L'air passe mieux. Mouchoir, puis poubelle. Côme va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Côme se lave les mains au robinet. L'eau est fraîche. Merci. Parce qu'il a pris un mouchoir, Côme respire mieux. Parce qu'il a jeté à la poubelle, ses mains sont prêtes à jouer. Ils arrosent les tomates. Côme sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Côme aide papa au jardin. Les fleurs sentent fort. Le pollen chatouille le nez de Côme. Son nez coule un peu. Papa ouvre la poche de son manteau. Papa tend un mouchoir. Côme prend un mouchoir. Le papier est doux. Il se mouche. Atchoum, tout doux. L'air passe mieux.
+papa|Mouchoir, puis poubelle.
+narrateur|Côme va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Côme se lave les mains au robinet. L'eau est fraîche.
+papa|Merci. Parce qu'il a pris un mouchoir, Côme respire mieux. Parce qu'il a jeté à la poubelle, ses mains sont prêtes à jouer. Ils arrosent les tomates.
+narrateur|Côme sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le nez de Côme chatouille. Que prend-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Côme a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Côme essuie ses mains. Papa range l'arrosoir. Le jardin sent la terre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Côme sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Le nez de Côme chatouille. Que prend-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Côme a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Côme essuie ses mains. Papa range l'arrosoir. Le jardin sent la terre.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Côme se mouche au jardin</t>
+          <t>Le mouchoir d'Aniss au jardin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'arrosoir goutte sur le chemin. Les tomates sentent vert. Le nez d'Aniss chatouille. Mouchoir, puis poubelle.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Côme aide papa au jardin. Les fleurs sentent fort. Le pollen chatouille le nez de Côme. Son nez coule un peu. Papa ouvre la poche de son manteau. Papa tend un mouchoir. Côme prend un mouchoir. Le papier est doux. Il se mouche. Atchoum, tout doux. L'air passe mieux. Mouchoir, puis poubelle. Côme va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Côme se lave les mains au robinet. L'eau est fraîche. Merci. Parce qu'il a pris un mouchoir, Côme respire mieux. Parce qu'il a jeté à la poubelle, ses mains sont prêtes à jouer. Ils arrosent les tomates. Côme sourit.</t>
+          <t>L'arrosoir goutte sur le chemin. Ça fait ploc, ploc, dans la terre. Les feuilles de tomates sentent vert. Une abeille tourne autour d'une fleur jaune. Le chapeau de papa attend sur le banc. Le banc est un peu chaud. Aniss, tu sens les tomates ? Oui, papa. Ça sent fort. L'arrosoir goutte encore. Ploc, ploc. En ce moment, Aniss aide papa. Il tient le tuyau tout doux. Les fleurs sentent fort. Le pollen chatouille le nez d'Aniss. Atchoum. Ton nez coule un peu ? Oui. Ça chatouille. Papa ouvre la poche de son manteau. Papa tend un mouchoir. Prends un mouchoir. Aniss prend un mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum, tout doux. L'air passe mieux. Je respire. Mouchoir, puis poubelle. Aniss va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Bravo. Tu as jeté le mouchoir. C'est du bon travail. Aniss se lave les mains au robinet. L'eau est fraîche. Tu as fini de laver tes mains ? Oui, papa. Merci. Parce que tu as pris un mouchoir. Tu respires mieux. Parce que tu as jeté à la poubelle. Tes mains sont prêtes à jouer. On arrose les tomates ? Oui. Tout doux. Ils arrosent les tomates. L'eau brille sur les feuilles. Ça sent encore vert. Oui. Et ton nez est calme. Mouchoir, poubelle. Oui. Bravo, Aniss. L'abeille s'en va. Le chapeau reste sur le banc. On met le chapeau ? Il est chaud. Le banc aussi. Aniss pose le chapeau sur sa tête. Une goutte d'eau brille sur une tomate. Elle brille. C'est l'eau de l'arrosoir. Le chemin est un peu mouillé. Les pieds d'Aniss restent sur les dalles. On range le tuyau, après. Après les tomates. Oui. Tes mains sont prêtes. Mes mains sont propres. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Côme aide papa au jardin. Les fleurs sentent fort. Le pollen chatouille le nez de Côme. Son nez coule un peu. Papa ouvre la poche de son manteau. Papa tend un mouchoir. Côme prend un mouchoir. Le papier est doux. Il se mouche. Atchoum, tout doux. L'air passe mieux.
+          <t>narrateur|L'arrosoir goutte sur le chemin.
+narrateur|Ça fait ploc, ploc, dans la terre.
+narrateur|Les feuilles de tomates sentent vert.
+narrateur|Une abeille tourne autour d'une fleur jaune.
+narrateur|Le chapeau de papa attend sur le banc.
+narrateur|Le banc est un peu chaud.
+papa|Aniss, tu sens les tomates ?
+enfant-m|Oui, papa. Ça sent fort.
+papa|L'arrosoir goutte encore.
+enfant-m|Ploc, ploc.
+narrateur|En ce moment, Aniss aide papa.
+narrateur|Il tient le tuyau tout doux.
+narrateur|Les fleurs sentent fort.
+narrateur|Le pollen chatouille le nez d'Aniss.
+enfant-m|Atchoum.
+papa|Ton nez coule un peu ?
+enfant-m|Oui. Ça chatouille.
+narrateur|Papa ouvre la poche de son manteau.
+narrateur|Papa tend un mouchoir.
+papa|Prends un mouchoir.
+narrateur|Aniss prend un mouchoir.
+narrateur|Le papier est doux.
+narrateur|Il se mouche, tout doux.
+enfant-m|Atchoum, tout doux.
+papa|L'air passe mieux.
+enfant-m|Je respire.
 papa|Mouchoir, puis poubelle.
-narrateur|Côme va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Côme se lave les mains au robinet. L'eau est fraîche.
-papa|Merci. Parce qu'il a pris un mouchoir, Côme respire mieux. Parce qu'il a jeté à la poubelle, ses mains sont prêtes à jouer. Ils arrosent les tomates.
-narrateur|Côme sourit.</t>
+narrateur|Aniss va jusqu'à la poubelle du jardin.
+narrateur|Il jette le mouchoir.
+narrateur|La poubelle fait un petit bruit.
+papa|Bravo. Tu as jeté le mouchoir.
+papa|C'est du bon travail.
+narrateur|Aniss se lave les mains au robinet.
+narrateur|L'eau est fraîche.
+papa|Tu as fini de laver tes mains ?
+enfant-m|Oui, papa.
+papa|Merci.
+papa|Parce que tu as pris un mouchoir.
+papa|Tu respires mieux.
+papa|Parce que tu as jeté à la poubelle.
+papa|Tes mains sont prêtes à jouer.
+enfant-m|On arrose les tomates ?
+papa|Oui. Tout doux.
+narrateur|Ils arrosent les tomates.
+narrateur|L'eau brille sur les feuilles.
+enfant-m|Ça sent encore vert.
+papa|Oui. Et ton nez est calme.
+enfant-m|Mouchoir, poubelle.
+papa|Oui. Bravo, Aniss.
+narrateur|L'abeille s'en va.
+narrateur|Le chapeau reste sur le banc.
+papa|On met le chapeau ?
+enfant-m|Il est chaud.
+papa|Le banc aussi.
+narrateur|Aniss pose le chapeau sur sa tête.
+narrateur|Une goutte d'eau brille sur une tomate.
+enfant-m|Elle brille.
+papa|C'est l'eau de l'arrosoir.
+narrateur|Le chemin est un peu mouillé.
+narrateur|Les pieds d'Aniss restent sur les dalles.
+papa|On range le tuyau, après.
+enfant-m|Après les tomates.
+papa|Oui. Tes mains sont prêtes.
+enfant-m|Mes mains sont propres.
+papa|Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>arrosoir</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le nez de Côme chatouille. Que prend-il ?</t>
+          <t>Le nez d'Aniss chatouille. Que prend-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1576,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le nez de Côme chatouille. Que prend-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le nez d'Aniss chatouille.
+narrateur|Que prend-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Côme a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Papa était là.</t>
+          <t>Aniss a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Bravo. C'est du bon travail. L'arrosoir ne goutte plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1748,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Côme a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Papa était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a pris un mouchoir.
+narrateur|Il s'est mouché.
+narrateur|Il a jeté le mouchoir à la poubelle.
+papa|Tu as pris un mouchoir ?
+enfant-m|Oui. Puis poubelle.
+papa|Bravo. C'est du bon travail.
+narrateur|L'arrosoir ne goutte plus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Côme essuie ses mains. Papa range l'arrosoir. Le jardin sent la terre.</t>
+          <t>Aniss essuie ses mains. Le torchon sent le soleil. On range l'arrosoir ? Oui, papa. Papa range l'arrosoir. Le jardin sent la terre. Mes mains sont sèches.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1921,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Côme essuie ses mains. Papa range l'arrosoir. Le jardin sent la terre.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Aniss essuie ses mains.
+narrateur|Le torchon sent le soleil.
+papa|On range l'arrosoir ?
+enfant-m|Oui, papa.
+narrateur|Papa range l'arrosoir.
+narrateur|Le jardin sent la terre.
+enfant-m|Mes mains sont sèches.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mouchoir, puis poubelle. Bravo, Aniss. Le chapeau reste sur le banc chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2094,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Mouchoir, puis poubelle.
+papa|Bravo, Aniss.
+narrateur|Le chapeau reste sur le banc chaud.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2156,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir goutte sur le chemin. Ça fait ploc, ploc, dans la terre. Les feuilles de tomates sentent vert. Une abeille tourne autour d'une fleur jaune. Le chapeau de papa attend sur le banc. Le banc est un peu chaud. Aniss, tu sens les tomates ? Oui, papa. Ça sent fort. L'arrosoir goutte encore. Ploc, ploc. En ce moment, Aniss aide papa. Il tient le tuyau tout doux. Les fleurs sentent fort. Le pollen chatouille le nez d'Aniss. Atchoum. Ton nez coule un peu ? Oui. Ça chatouille. Papa ouvre la poche de son manteau. Papa tend un mouchoir. Prends un mouchoir. Aniss prend un mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum, tout doux. L'air passe mieux. Je respire. Mouchoir, puis poubelle. Aniss va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Bravo. Tu as jeté le mouchoir. C'est du bon travail. Aniss se lave les mains au robinet. L'eau est fraîche. Tu as fini de laver tes mains ? Oui, papa. Merci. Parce que tu as pris un mouchoir. Tu respires mieux. Parce que tu as jeté à la poubelle. Tes mains sont prêtes à jouer. On arrose les tomates ? Oui. Tout doux. Ils arrosent les tomates. L'eau brille sur les feuilles. Ça sent encore vert. Oui. Et ton nez est calme. Mouchoir, poubelle. Oui. Bravo, Aniss. L'abeille s'en va. Le chapeau reste sur le banc. On met le chapeau ? Il est chaud. Le banc aussi. Aniss pose le chapeau sur sa tête. Une goutte d'eau brille sur une tomate. Elle brille. C'est l'eau de l'arrosoir. Le chemin est un peu mouillé. Les pieds d'Aniss restent sur les dalles. On range le tuyau, après. Après les tomates. Oui. Tes mains sont prêtes. Mes mains sont propres. Bravo. C'est du bon travail.</t>
+          <t>L'arrosoir goutte sur le chemin. Ça fait ploc, ploc, dans la terre. Les feuilles de tomates sentent vert. Une abeille tourne autour d'une fleur jaune. Le chapeau de papa attend sur le banc. Le banc est un peu chaud. Aniss, tu sens les tomates ? Oui, papa. Ça sent fort. L'arrosoir goutte encore. Ploc, ploc. En ce moment, Aniss aide papa. Il tient le tuyau tout doux. Les fleurs sentent fort. Le pollen chatouille le nez d'Aniss. Atchoum. Ton nez coule un peu ? Oui. Ça chatouille. Papa ouvre la poche de son manteau. Papa tend un mouchoir. Prends un mouchoir. Aniss prend un mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum, tout doux. L'air passe mieux. Je respire. Mouchoir, puis poubelle. Aniss va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Bravo. Tu as jeté le mouchoir. Aniss se lave les mains au robinet. L'eau est fraîche. Tu as fini de laver tes mains ? Oui, papa. Merci. Parce que tu as pris un mouchoir. Tu respires mieux. Parce que tu as jeté à la poubelle. Tes mains sont prêtes à jouer. On arrose les tomates ? Oui. Tout doux. Ils arrosent les tomates. L'eau brille sur les feuilles. Ça sent encore vert. Oui. Et ton nez est calme. Mouchoir, poubelle. Oui. Bravo, Aniss. L'abeille s'en va. Le chapeau reste sur le banc. On met le chapeau ? Il est chaud. Le banc aussi. Aniss pose le chapeau sur sa tête. Une goutte d'eau brille sur une tomate. Elle brille. C'est l'eau de l'arrosoir. Le chemin est un peu mouillé. Les pieds d'Aniss restent sur les dalles. On range le tuyau, après. Après les tomates. Oui. Tes mains sont prêtes. Mes mains sont propres.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Côme aide papa au jardin. Les fleurs sentent fort. Le pollen chatouille le nez de Côme. Son nez coule un peu. Papa ouvre la poche de son manteau. Papa tend un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Côme prend un mouchoir. Le papier est doux. Il se mouche. Atchoum, tout doux. L'air passe mieux. Papa dit : mouchoir, puis poubelle. Côme va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Côme se lave les mains au robinet. L'eau est fraîche. Papa dit : merci. Parce qu'il a pris un mouchoir, Côme respire mieux. Parce qu'il a jeté à la poubelle, ses mains sont prêtes à jouer. Ils arrosent les tomates. Côme sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir goutte sur le chemin. Ça fait ploc, ploc, dans la terre. Les feuilles de tomates sentent vert. Une abeille tourne autour d'une fleur jaune. Le chapeau de papa attend sur le banc. Le banc est un peu chaud. Aniss, tu sens les tomates ? Oui, papa. Ça sent fort. L'arrosoir goutte encore. Ploc, ploc. En ce moment, Aniss aide papa. Il tient le tuyau tout doux. Les fleurs sentent fort. Le pollen chatouille le nez d'Aniss. Atchoum. Ton nez coule un peu ? Oui. Ça chatouille. Papa ouvre la poche de son manteau. Papa tend un mouchoir. Prends un mouchoir. Aniss prend un mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum, tout doux. L'air passe mieux. Je respire. Mouchoir, puis poubelle. Aniss va jusqu'à la poubelle du jardin. Il jette le mouchoir. La poubelle fait un petit bruit. Bravo. Tu as jeté le mouchoir. Aniss se lave les mains au robinet. L'eau est fraîche. Tu as fini de laver tes mains ? Oui, papa. Merci. Parce que tu as pris un mouchoir. Tu respires mieux. Parce que tu as jeté à la poubelle. Tes mains sont prêtes à jouer. On arrose les tomates ? Oui. Tout doux. Ils arrosent les tomates. L'eau brille sur les feuilles. Ça sent encore vert. Oui. Et ton nez est calme. Mouchoir, poubelle. Oui. Bravo, Aniss. L'abeille s'en va. Le chapeau reste sur le banc. On met le chapeau ? Il est chaud. Le banc aussi. Aniss pose le chapeau sur sa tête. Une goutte d'eau brille sur une tomate. Elle brille. C'est l'eau de l'arrosoir. Le chemin est un peu mouillé. Les pieds d'Aniss restent sur les dalles. On range le tuyau, après. Après les tomates. Oui. Tes mains sont prêtes. Mes mains sont propres.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1355,7 +1355,6 @@
 narrateur|Il jette le mouchoir.
 narrateur|La poubelle fait un petit bruit.
 papa|Bravo. Tu as jeté le mouchoir.
-papa|C'est du bon travail.
 narrateur|Aniss se lave les mains au robinet.
 narrateur|L'eau est fraîche.
 papa|Tu as fini de laver tes mains ?
@@ -1387,8 +1386,7 @@
 papa|On range le tuyau, après.
 enfant-m|Après les tomates.
 papa|Oui. Tes mains sont prêtes.
-enfant-m|Mes mains sont propres.
-papa|Bravo. C'est du bon travail.</t>
+enfant-m|Mes mains sont propres.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1425,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le nez de Côme chatouille. Que prend-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le nez d'Aniss chatouille. Que prend-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1604,12 +1602,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Bravo. C'est du bon travail. L'arrosoir ne goutte plus.</t>
+          <t>Aniss a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. L'arrosoir ne goutte plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Côme a pris un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. L'arrosoir ne goutte plus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1753,7 +1751,6 @@
 narrateur|Il a jeté le mouchoir à la poubelle.
 papa|Tu as pris un mouchoir ?
 enfant-m|Oui. Puis poubelle.
-papa|Bravo. C'est du bon travail.
 narrateur|L'arrosoir ne goutte plus.</t>
         </is>
       </c>
@@ -1786,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Côme essuie ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Papa range l'arrosoir. Le jardin sent la terre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss essuie ses mains. Le torchon sent le soleil. On range l'arrosoir ? Oui, papa. Papa range l'arrosoir. Le jardin sent la terre. Mes mains sont sèches.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1954,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mouchoir, puis poubelle. Bravo, Aniss. Le chapeau reste sur le banc chaud. L'histoire est finie.</t>
+          <t>Mouchoir, puis poubelle. Bravo, Aniss. Le chapeau reste sur le banc chaud.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mouchoir, puis poubelle. Bravo, Aniss. Le chapeau reste sur le banc chaud.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,8 +2093,7 @@
         <is>
           <t>enfant-m|Mouchoir, puis poubelle.
 papa|Bravo, Aniss.
-narrateur|Le chapeau reste sur le banc chaud.
-narrateur|L'histoire est finie.</t>
+narrateur|Le chapeau reste sur le banc chaud.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2163,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, arrosoir, tomates, poubelle du jardin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Côme, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
